--- a/unified_metrics_xgb.xlsx
+++ b/unified_metrics_xgb.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0186653/Desktop/research/dingen/deepnir/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439E4909-BADE-2648-A447-0A7179F16DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -97,12 +103,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,15 +145,34 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +210,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -219,6 +244,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -253,9 +279,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -428,20 +455,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,7 +491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -475,19 +502,19 @@
         <v>24</v>
       </c>
       <c r="D2" s="1">
-        <v>0.8585811928364946</v>
+        <v>0.85858119283649459</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0355447507807403</v>
+        <v>3.5544750780740299E-2</v>
       </c>
       <c r="F2" s="2">
         <v>12.08943016803439</v>
       </c>
       <c r="G2" s="2">
-        <v>-0.0440291985221531</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>-4.4029198522153097E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -498,19 +525,19 @@
         <v>24</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.1993661970421065</v>
+        <v>-0.19936619704210651</v>
       </c>
       <c r="E3" s="2">
-        <v>0.1821838344730476</v>
+        <v>0.18218383447304759</v>
       </c>
       <c r="F3" s="2">
-        <v>0.1469635760170312</v>
+        <v>0.14696357601703119</v>
       </c>
       <c r="G3" s="2">
         <v>-0.1084353046427407</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -521,19 +548,19 @@
         <v>24</v>
       </c>
       <c r="D4" s="1">
-        <v>0.723114443240693</v>
+        <v>0.72311444324069296</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0546435251868701</v>
+        <v>5.4643525186870101E-2</v>
       </c>
       <c r="F4" s="2">
         <v>6.01115622429257</v>
       </c>
       <c r="G4" s="2">
-        <v>-0.0323772591401433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>-3.2377259140143298E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -544,19 +571,19 @@
         <v>24</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8553064617976084</v>
+        <v>0.85530646179760839</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0363678343647829</v>
+        <v>3.63678343647829E-2</v>
       </c>
       <c r="F5" s="2">
         <v>10.7787627395405</v>
       </c>
       <c r="G5" s="2">
-        <v>-0.0247461940931237</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>-2.4746194093123699E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -567,19 +594,19 @@
         <v>24</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8431845420861682</v>
+        <v>0.84318454208616822</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0309476215534561</v>
+        <v>3.0947621553456098E-2</v>
       </c>
       <c r="F6" s="2">
         <v>10.84737679606538</v>
       </c>
       <c r="G6" s="2">
-        <v>-0.0604192122724093</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>-6.0419212272409303E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -590,19 +617,19 @@
         <v>24</v>
       </c>
       <c r="D7" s="1">
-        <v>0.4629516281187493</v>
+        <v>0.46295162811874929</v>
       </c>
       <c r="E7" s="2">
-        <v>0.0815776965601762</v>
+        <v>8.1577696560176202E-2</v>
       </c>
       <c r="F7" s="2">
-        <v>4.659237331532792</v>
+        <v>4.6592373315327924</v>
       </c>
       <c r="G7" s="2">
-        <v>0.039821791965739</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>3.9821791965738998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -613,19 +640,19 @@
         <v>25</v>
       </c>
       <c r="D8" s="1">
-        <v>0.7836867278936209</v>
+        <v>0.78368672789362093</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0543690157045242</v>
+        <v>5.4369015704524203E-2</v>
       </c>
       <c r="F8" s="2">
-        <v>6.088531743496578</v>
+        <v>6.0885317434965778</v>
       </c>
       <c r="G8" s="2">
-        <v>-0.0213768627332605</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>-2.1376862733260501E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -639,16 +666,16 @@
         <v>0.1963160978914745</v>
       </c>
       <c r="E9" s="2">
-        <v>0.1220796578655386</v>
+        <v>0.12207965786553859</v>
       </c>
       <c r="F9" s="2">
-        <v>0.4096565040418961</v>
+        <v>0.40965650404189607</v>
       </c>
       <c r="G9" s="2">
-        <v>-0.09719784228108699</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>-9.7197842281086994E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -662,16 +689,16 @@
         <v>0.5125858626096047</v>
       </c>
       <c r="E10" s="2">
-        <v>0.096191462655747</v>
+        <v>9.6191462655747004E-2</v>
       </c>
       <c r="F10" s="2">
-        <v>1.927456882526858</v>
+        <v>1.9274568825268581</v>
       </c>
       <c r="G10" s="2">
-        <v>0.0178362935164845</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>1.7836293516484501E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -682,19 +709,19 @@
         <v>25</v>
       </c>
       <c r="D11" s="1">
-        <v>0.8439589570106886</v>
+        <v>0.84395895701068857</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0392199601726889</v>
+        <v>3.9219960172688903E-2</v>
       </c>
       <c r="F11" s="2">
         <v>10.25784896230779</v>
       </c>
       <c r="G11" s="2">
-        <v>0.0066989774289337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>6.6989774289337002E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -705,19 +732,19 @@
         <v>25</v>
       </c>
       <c r="D12" s="1">
-        <v>0.765646298974247</v>
+        <v>0.76564629897424696</v>
       </c>
       <c r="E12" s="2">
-        <v>0.046249838794477</v>
+        <v>4.6249838794477E-2</v>
       </c>
       <c r="F12" s="2">
-        <v>7.04354408602794</v>
+        <v>7.0435440860279401</v>
       </c>
       <c r="G12" s="2">
-        <v>-0.0297163602049161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>-2.9716360204916099E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -728,19 +755,19 @@
         <v>25</v>
       </c>
       <c r="D13" s="1">
-        <v>0.7510671055744408</v>
+        <v>0.75106710557444079</v>
       </c>
       <c r="E13" s="2">
-        <v>0.0378129293161415</v>
+        <v>3.7812929316141497E-2</v>
       </c>
       <c r="F13" s="2">
-        <v>6.603067082638402</v>
+        <v>6.6030670826384021</v>
       </c>
       <c r="G13" s="2">
-        <v>-0.0717824217488605</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>-7.17824217488605E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -751,19 +778,19 @@
         <v>25</v>
       </c>
       <c r="D14" s="1">
-        <v>0.7510671055744408</v>
+        <v>0.75106710557444079</v>
       </c>
       <c r="E14" s="2">
-        <v>0.0378129293161415</v>
+        <v>3.7812929316141497E-2</v>
       </c>
       <c r="F14" s="2">
-        <v>6.603067082638402</v>
+        <v>6.6030670826384021</v>
       </c>
       <c r="G14" s="2">
-        <v>-0.0717824217488605</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>-7.17824217488605E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -774,19 +801,19 @@
         <v>24</v>
       </c>
       <c r="D15" s="1">
-        <v>0.6961504227705825</v>
+        <v>0.69615042277058248</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0110322974919708</v>
+        <v>1.1032297491970801E-2</v>
       </c>
       <c r="F15" s="2">
-        <v>9.8174285268398</v>
+        <v>9.8174285268397998</v>
       </c>
       <c r="G15" s="2">
-        <v>0.0066068168089305</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>6.6068168089304996E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -797,19 +824,19 @@
         <v>24</v>
       </c>
       <c r="D16" s="1">
-        <v>0.4470411294711324</v>
+        <v>0.44704112947113239</v>
       </c>
       <c r="E16" s="2">
-        <v>0.0103179364814859</v>
+        <v>1.03179364814859E-2</v>
       </c>
       <c r="F16" s="2">
-        <v>7.635278954114781</v>
+        <v>7.6352789541147814</v>
       </c>
       <c r="G16" s="2">
-        <v>0.0203287502141662</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>2.0328750214166202E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -823,16 +850,16 @@
         <v>0.6516683646167456</v>
       </c>
       <c r="E17" s="2">
-        <v>0.0231217616339999</v>
+        <v>2.3121761633999899E-2</v>
       </c>
       <c r="F17" s="2">
-        <v>5.858989208765117</v>
+        <v>5.8589892087651174</v>
       </c>
       <c r="G17" s="2">
-        <v>0.0006518919612339</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>6.5189196123390002E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -846,16 +873,16 @@
         <v>0.3685185346418457</v>
       </c>
       <c r="E18" s="2">
-        <v>0.007960431073393</v>
+        <v>7.9604310733930005E-3</v>
       </c>
       <c r="F18" s="2">
-        <v>8.487029328788871</v>
+        <v>8.4870293287888714</v>
       </c>
       <c r="G18" s="2">
-        <v>-0.0208403469045379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>-2.0840346904537899E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -866,19 +893,19 @@
         <v>24</v>
       </c>
       <c r="D19" s="1">
-        <v>0.3019877197060271</v>
+        <v>0.30198771970602711</v>
       </c>
       <c r="E19" s="2">
-        <v>0.0130245606955941</v>
+        <v>1.3024560695594101E-2</v>
       </c>
       <c r="F19" s="2">
-        <v>11.54603105941056</v>
+        <v>11.546031059410559</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.02188964618459</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>-2.1889646184590002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -889,19 +916,19 @@
         <v>24</v>
       </c>
       <c r="D20" s="1">
-        <v>0.439516161327287</v>
+        <v>0.43951616132728699</v>
       </c>
       <c r="E20" s="2">
-        <v>0.02035028155728</v>
+        <v>2.0350281557280001E-2</v>
       </c>
       <c r="F20" s="2">
         <v>5.945165463515135</v>
       </c>
       <c r="G20" s="2">
-        <v>0.0525235784797243</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>5.2523578479724303E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -912,19 +939,19 @@
         <v>24</v>
       </c>
       <c r="D21" s="1">
-        <v>0.0314708999463084</v>
+        <v>3.1470899946308403E-2</v>
       </c>
       <c r="E21" s="2">
-        <v>0.0122092405977109</v>
+        <v>1.22092405977109E-2</v>
       </c>
       <c r="F21" s="2">
-        <v>11.21014026880606</v>
+        <v>11.210140268806059</v>
       </c>
       <c r="G21" s="2">
-        <v>0.0113630137032115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>1.1363013703211499E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -935,19 +962,19 @@
         <v>24</v>
       </c>
       <c r="D22" s="1">
-        <v>0.4855485882039826</v>
+        <v>0.48554858820398261</v>
       </c>
       <c r="E22" s="2">
-        <v>0.0341485576029713</v>
+        <v>3.4148557602971301E-2</v>
       </c>
       <c r="F22" s="2">
-        <v>5.16599654811103</v>
+        <v>5.1659965481110302</v>
       </c>
       <c r="G22" s="2">
-        <v>-0.0443465494624547</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>-4.4346549462454699E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -958,19 +985,19 @@
         <v>25</v>
       </c>
       <c r="D23" s="1">
-        <v>0.7140794961345197</v>
+        <v>0.71407949613451971</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0103813211999848</v>
+        <v>1.03813211999848E-2</v>
       </c>
       <c r="F23" s="2">
         <v>10.51719722261643</v>
       </c>
       <c r="G23" s="2">
-        <v>0.0106863289963433</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>1.06863289963433E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -981,19 +1008,19 @@
         <v>25</v>
       </c>
       <c r="D24" s="1">
-        <v>0.3880762953598353</v>
+        <v>0.38807629535983529</v>
       </c>
       <c r="E24" s="2">
-        <v>0.0114181908501695</v>
+        <v>1.1418190850169501E-2</v>
       </c>
       <c r="F24" s="2">
-        <v>8.813814483684332</v>
+        <v>8.8138144836843324</v>
       </c>
       <c r="G24" s="2">
-        <v>0.0364208969816765</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>3.6420896981676498E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1004,19 +1031,19 @@
         <v>25</v>
       </c>
       <c r="D25" s="1">
-        <v>0.5453775912683514</v>
+        <v>0.54537759126835139</v>
       </c>
       <c r="E25" s="2">
-        <v>0.0301771929402925</v>
+        <v>3.0177192940292499E-2</v>
       </c>
       <c r="F25" s="2">
-        <v>4.471194276666499</v>
+        <v>4.4711942766664992</v>
       </c>
       <c r="G25" s="2">
-        <v>-0.0042969624851772</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>-4.2969624851772002E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1030,16 +1057,16 @@
         <v>0.3114961932616418</v>
       </c>
       <c r="E26" s="2">
-        <v>0.0086792525164628</v>
+        <v>8.6792525164627998E-3</v>
       </c>
       <c r="F26" s="2">
-        <v>7.62353177835433</v>
+        <v>7.6235317783543302</v>
       </c>
       <c r="G26" s="2">
-        <v>-0.0187513107661038</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>-1.8751310766103799E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1050,19 +1077,19 @@
         <v>25</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.0147329799799853</v>
+        <v>-1.47329799799853E-2</v>
       </c>
       <c r="E27" s="2">
-        <v>0.0189344108416032</v>
+        <v>1.8934410841603199E-2</v>
       </c>
       <c r="F27" s="2">
-        <v>8.263552634518462</v>
+        <v>8.2635526345184616</v>
       </c>
       <c r="G27" s="2">
-        <v>0.0143874572394822</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>1.4387457239482201E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1073,19 +1100,19 @@
         <v>25</v>
       </c>
       <c r="D28" s="1">
-        <v>0.7290788236511609</v>
+        <v>0.72907882365116095</v>
       </c>
       <c r="E28" s="2">
-        <v>0.0098367193451724</v>
+        <v>9.8367193451724001E-3</v>
       </c>
       <c r="F28" s="2">
-        <v>13.31822803509131</v>
+        <v>13.318228035091311</v>
       </c>
       <c r="G28" s="2">
-        <v>0.0242488243642109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>2.42488243642109E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1096,19 +1123,19 @@
         <v>25</v>
       </c>
       <c r="D29" s="1">
-        <v>0.184526361305331</v>
+        <v>0.18452636130533101</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0102798293364258</v>
+        <v>1.0279829336425799E-2</v>
       </c>
       <c r="F29" s="2">
-        <v>11.4396482919634</v>
+        <v>11.439648291963399</v>
       </c>
       <c r="G29" s="2">
-        <v>0.014534808996116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>1.4534808996116E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1119,19 +1146,19 @@
         <v>25</v>
       </c>
       <c r="D30" s="1">
-        <v>0.0389812876461836</v>
+        <v>3.8981287646183603E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>0.063791063847561</v>
+        <v>6.3791063847561003E-2</v>
       </c>
       <c r="F30" s="2">
         <v>3.637078726288749</v>
       </c>
       <c r="G30" s="2">
-        <v>-0.020790078591483</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>-2.0790078591483001E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1142,19 +1169,19 @@
         <v>25</v>
       </c>
       <c r="D31" s="1">
-        <v>0.0389812876461836</v>
+        <v>3.8981287646183603E-2</v>
       </c>
       <c r="E31" s="2">
-        <v>0.063791063847561</v>
+        <v>6.3791063847561003E-2</v>
       </c>
       <c r="F31" s="2">
         <v>3.637078726288749</v>
       </c>
       <c r="G31" s="2">
-        <v>-0.020790078591483</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>-2.0790078591483001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -1168,16 +1195,16 @@
         <v>0.903354649570282</v>
       </c>
       <c r="E32" s="2">
-        <v>0.0780412251561106</v>
+        <v>7.8041225156110602E-2</v>
       </c>
       <c r="F32" s="2">
         <v>11.03398388657445</v>
       </c>
       <c r="G32" s="2">
-        <v>0.0044037805664053</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>4.4037805664052998E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -1188,19 +1215,19 @@
         <v>24</v>
       </c>
       <c r="D33" s="1">
-        <v>0.9922340879886949</v>
+        <v>0.99223408798869495</v>
       </c>
       <c r="E33" s="2">
-        <v>0.0387574401912423</v>
+        <v>3.8757440191242297E-2</v>
       </c>
       <c r="F33" s="2">
-        <v>57.41152235275623</v>
+        <v>57.411522352756229</v>
       </c>
       <c r="G33" s="2">
-        <v>-0.0609333351258685</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>-6.0933335125868501E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -1211,19 +1238,19 @@
         <v>24</v>
       </c>
       <c r="D34" s="1">
-        <v>0.9044821939019412</v>
+        <v>0.90448219390194118</v>
       </c>
       <c r="E34" s="2">
         <v>0.1045944533497374</v>
       </c>
       <c r="F34" s="2">
-        <v>8.018843765438355</v>
+        <v>8.0188437654383549</v>
       </c>
       <c r="G34" s="2">
-        <v>-0.0300929297314468</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>-3.00929297314468E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -1234,19 +1261,19 @@
         <v>24</v>
       </c>
       <c r="D35" s="1">
-        <v>0.9978948560101626</v>
+        <v>0.99789485601016259</v>
       </c>
       <c r="E35" s="2">
-        <v>0.0166463998951226</v>
+        <v>1.66463998951226E-2</v>
       </c>
       <c r="F35" s="2">
-        <v>167.3878928373863</v>
+        <v>167.38789283738629</v>
       </c>
       <c r="G35" s="2">
-        <v>0.0116353668370851</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>1.16353668370851E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -1257,19 +1284,19 @@
         <v>24</v>
       </c>
       <c r="D36" s="1">
-        <v>0.9862667961970152</v>
+        <v>0.98626679619701518</v>
       </c>
       <c r="E36" s="2">
-        <v>0.0425799993718049</v>
+        <v>4.25799993718049E-2</v>
       </c>
       <c r="F36" s="2">
-        <v>38.8969614814139</v>
+        <v>38.896961481413904</v>
       </c>
       <c r="G36" s="2">
-        <v>0.0281439830566404</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>2.8143983056640402E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -1280,19 +1307,19 @@
         <v>24</v>
       </c>
       <c r="D37" s="1">
-        <v>0.9953319468862338</v>
+        <v>0.99533194688623383</v>
       </c>
       <c r="E37" s="2">
-        <v>0.0232969146576683</v>
+        <v>2.32969146576683E-2</v>
       </c>
       <c r="F37" s="2">
-        <v>94.7411892528216</v>
+        <v>94.741189252821599</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.0280369117860247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>-2.8036911786024701E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -1303,19 +1330,19 @@
         <v>24</v>
       </c>
       <c r="D38" s="1">
-        <v>0.8980139325862755</v>
+        <v>0.89801393258627549</v>
       </c>
       <c r="E38" s="2">
-        <v>0.0823538599056427</v>
+        <v>8.2353859905642701E-2</v>
       </c>
       <c r="F38" s="2">
-        <v>10.34835204006004</v>
+        <v>10.348352040060041</v>
       </c>
       <c r="G38" s="2">
-        <v>0.024704509500557</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>2.4704509500557002E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -1326,19 +1353,19 @@
         <v>24</v>
       </c>
       <c r="D39" s="1">
-        <v>0.9815211816433256</v>
+        <v>0.98152118164332558</v>
       </c>
       <c r="E39" s="2">
-        <v>0.0572938467459339</v>
+        <v>5.72938467459339E-2</v>
       </c>
       <c r="F39" s="2">
-        <v>28.63456449184383</v>
+        <v>28.634564491843829</v>
       </c>
       <c r="G39" s="2">
-        <v>0.0567101462183457</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>5.6710146218345699E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -1349,19 +1376,19 @@
         <v>24</v>
       </c>
       <c r="D40" s="1">
-        <v>0.9944108159511476</v>
+        <v>0.99441081595114755</v>
       </c>
       <c r="E40" s="2">
-        <v>0.0441964032929745</v>
+        <v>4.4196403292974501E-2</v>
       </c>
       <c r="F40" s="2">
-        <v>58.56720314975893</v>
+        <v>58.567203149758932</v>
       </c>
       <c r="G40" s="2">
-        <v>-0.0502026709903505</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>-5.0202670990350501E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -1372,19 +1399,19 @@
         <v>24</v>
       </c>
       <c r="D41" s="1">
-        <v>0.9316847719019652</v>
+        <v>0.93168477190196519</v>
       </c>
       <c r="E41" s="2">
-        <v>0.07480693108718479</v>
+        <v>7.4806931087184794E-2</v>
       </c>
       <c r="F41" s="2">
-        <v>11.85820867348323</v>
+        <v>11.858208673483229</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.0697818030224624</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>-6.9781803022462396E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -1395,19 +1422,19 @@
         <v>25</v>
       </c>
       <c r="D42" s="1">
-        <v>0.8909169421217532</v>
+        <v>0.89091694212175321</v>
       </c>
       <c r="E42" s="2">
-        <v>0.08808468739304801</v>
+        <v>8.8084687393048006E-2</v>
       </c>
       <c r="F42" s="2">
-        <v>9.242343838360711</v>
+        <v>9.2423438383607106</v>
       </c>
       <c r="G42" s="2">
-        <v>-0.016172478501675</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>-1.6172478501675001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1418,19 +1445,19 @@
         <v>25</v>
       </c>
       <c r="D43" s="1">
-        <v>0.9931147109894564</v>
+        <v>0.99311471098945636</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0343625032883572</v>
+        <v>3.4362503288357202E-2</v>
       </c>
       <c r="F43" s="2">
-        <v>64.0724970066382</v>
+        <v>64.072497006638201</v>
       </c>
       <c r="G43" s="2">
-        <v>-0.0692344554600699</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>-6.9234455460069899E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -1441,19 +1468,19 @@
         <v>25</v>
       </c>
       <c r="D44" s="1">
-        <v>0.9223289757832496</v>
+        <v>0.92232897578324957</v>
       </c>
       <c r="E44" s="2">
-        <v>0.08505176836583909</v>
+        <v>8.5051768365839095E-2</v>
       </c>
       <c r="F44" s="2">
-        <v>9.978271639456439</v>
+        <v>9.9782716394564392</v>
       </c>
       <c r="G44" s="2">
-        <v>-0.0177687872753921</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>-1.7768787275392099E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -1464,19 +1491,19 @@
         <v>25</v>
       </c>
       <c r="D45" s="1">
-        <v>0.9980511353384948</v>
+        <v>0.99805113533849477</v>
       </c>
       <c r="E45" s="2">
-        <v>0.0154106230516775</v>
+        <v>1.5410623051677501E-2</v>
       </c>
       <c r="F45" s="2">
-        <v>176.5215838097573</v>
+        <v>176.52158380975729</v>
       </c>
       <c r="G45" s="2">
-        <v>-0.0033083731100656</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>-3.3083731100656002E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -1487,19 +1514,19 @@
         <v>25</v>
       </c>
       <c r="D46" s="1">
-        <v>0.983616682547775</v>
+        <v>0.98361668254777501</v>
       </c>
       <c r="E46" s="2">
-        <v>0.050796715524763</v>
+        <v>5.0796715524763003E-2</v>
       </c>
       <c r="F46" s="2">
-        <v>32.63084919169999</v>
+        <v>32.630849191699987</v>
       </c>
       <c r="G46" s="2">
-        <v>0.0334912678340515</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>3.34912678340515E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -1510,19 +1537,19 @@
         <v>25</v>
       </c>
       <c r="D47" s="1">
-        <v>0.9921308476711824</v>
+        <v>0.99213084767118243</v>
       </c>
       <c r="E47" s="2">
-        <v>0.0392726830146857</v>
+        <v>3.92726830146857E-2</v>
       </c>
       <c r="F47" s="2">
-        <v>56.76354904320675</v>
+        <v>56.763549043206751</v>
       </c>
       <c r="G47" s="2">
-        <v>-0.0233070262608511</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>-2.3307026260851099E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -1533,19 +1560,19 @@
         <v>25</v>
       </c>
       <c r="D48" s="1">
-        <v>0.902442279662952</v>
+        <v>0.90244227966295198</v>
       </c>
       <c r="E48" s="2">
-        <v>0.0787779648445384</v>
+        <v>7.8777964844538403E-2</v>
       </c>
       <c r="F48" s="2">
-        <v>10.34005311492663</v>
+        <v>10.340053114926629</v>
       </c>
       <c r="G48" s="2">
-        <v>-0.0159350953404027</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>-1.5935095340402699E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -1556,19 +1583,19 @@
         <v>25</v>
       </c>
       <c r="D49" s="1">
-        <v>0.9764597291729418</v>
+        <v>0.97645972917294177</v>
       </c>
       <c r="E49" s="2">
-        <v>0.0729869542029512</v>
+        <v>7.2986954202951204E-2</v>
       </c>
       <c r="F49" s="2">
-        <v>22.47792710371593</v>
+        <v>22.477927103715931</v>
       </c>
       <c r="G49" s="2">
-        <v>0.0733970790123247</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>7.3397079012324701E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -1579,19 +1606,19 @@
         <v>25</v>
       </c>
       <c r="D50" s="1">
-        <v>0.9964167291707012</v>
+        <v>0.99641672917070123</v>
       </c>
       <c r="E50" s="2">
-        <v>0.0283346694786617</v>
+        <v>2.83346694786617E-2</v>
       </c>
       <c r="F50" s="2">
-        <v>96.37670420789946</v>
+        <v>96.376704207899465</v>
       </c>
       <c r="G50" s="2">
-        <v>-0.0395094013729332</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>-3.9509401372933198E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -1602,19 +1629,19 @@
         <v>25</v>
       </c>
       <c r="D51" s="1">
-        <v>0.9349715607791572</v>
+        <v>0.93497156077915722</v>
       </c>
       <c r="E51" s="2">
-        <v>0.0712078127664295</v>
+        <v>7.1207812766429499E-2</v>
       </c>
       <c r="F51" s="2">
         <v>12.79308146978464</v>
       </c>
       <c r="G51" s="2">
-        <v>-0.0654170264111343</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>-6.5417026411134296E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -1625,19 +1652,19 @@
         <v>25</v>
       </c>
       <c r="D52" s="1">
-        <v>0.9349715607791572</v>
+        <v>0.93497156077915722</v>
       </c>
       <c r="E52" s="2">
-        <v>0.0712078127664295</v>
+        <v>7.1207812766429499E-2</v>
       </c>
       <c r="F52" s="2">
         <v>12.79308146978464</v>
       </c>
       <c r="G52" s="2">
-        <v>-0.0654170264111343</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>-6.5417026411134296E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -1648,19 +1675,19 @@
         <v>24</v>
       </c>
       <c r="D53" s="1">
-        <v>0.3428465373379846</v>
+        <v>0.34284653733798459</v>
       </c>
       <c r="E53" s="2">
-        <v>0.5185538232642085</v>
+        <v>0.51855382326420851</v>
       </c>
       <c r="F53" s="2">
-        <v>0.4704076988277773</v>
+        <v>0.47040769882777728</v>
       </c>
       <c r="G53" s="2">
-        <v>-0.0622919331426202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>-6.2291933142620201E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -1671,10 +1698,10 @@
         <v>24</v>
       </c>
       <c r="D54" s="1">
-        <v>0.9540830492737664</v>
+        <v>0.95408304927376641</v>
       </c>
       <c r="E54" s="2">
-        <v>0.1726461830997656</v>
+        <v>0.17264618309976559</v>
       </c>
       <c r="F54" s="2">
         <v>10.02054220175866</v>
@@ -1683,7 +1710,7 @@
         <v>-0.2348332335765691</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -1694,19 +1721,19 @@
         <v>24</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.4855337458336568</v>
+        <v>-0.48553374583365683</v>
       </c>
       <c r="E55" s="2">
-        <v>2.154964742758415</v>
+        <v>2.1549647427584149</v>
       </c>
       <c r="F55" s="2">
-        <v>0.0199432504232061</v>
+        <v>1.9943250423206101E-2</v>
       </c>
       <c r="G55" s="2">
-        <v>0.7421013878417965</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>0.74210138784179647</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -1717,19 +1744,19 @@
         <v>24</v>
       </c>
       <c r="D56" s="1">
-        <v>0.9246629062312228</v>
+        <v>0.92466290623122283</v>
       </c>
       <c r="E56" s="2">
-        <v>0.0172002648452248</v>
+        <v>1.72002648452248E-2</v>
       </c>
       <c r="F56" s="2">
-        <v>22.29466492580137</v>
+        <v>22.294664925801371</v>
       </c>
       <c r="G56" s="2">
-        <v>-0.047517019228906</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>-4.7517019228905999E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -1740,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="D57" s="1">
-        <v>0.9703788199812354</v>
+        <v>0.97037881998123543</v>
       </c>
       <c r="E57" s="2">
         <v>0.1113746359082378</v>
@@ -1749,10 +1776,10 @@
         <v>15.73281020723409</v>
       </c>
       <c r="G57" s="2">
-        <v>-0.1352150529837143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>-0.13521505298371431</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -1763,19 +1790,19 @@
         <v>24</v>
       </c>
       <c r="D58" s="1">
-        <v>0.8353780789702419</v>
+        <v>0.83537807897024186</v>
       </c>
       <c r="E58" s="2">
         <v>0.1299016613216637</v>
       </c>
       <c r="F58" s="2">
-        <v>4.600318960398685</v>
+        <v>4.6003189603986847</v>
       </c>
       <c r="G58" s="2">
-        <v>-0.0137136708135187</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>-1.3713670813518699E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -1786,19 +1813,19 @@
         <v>24</v>
       </c>
       <c r="D59" s="1">
-        <v>0.9789403757400436</v>
+        <v>0.97894037574004356</v>
       </c>
       <c r="E59" s="2">
-        <v>0.0048081376210758</v>
+        <v>4.8081376210757998E-3</v>
       </c>
       <c r="F59" s="2">
-        <v>93.88325656075686</v>
+        <v>93.883256560756863</v>
       </c>
       <c r="G59" s="2">
-        <v>0.0199145896069501</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>1.9914589606950101E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -1809,19 +1836,19 @@
         <v>24</v>
       </c>
       <c r="D60" s="1">
-        <v>0.8476423098095983</v>
+        <v>0.84764230980959832</v>
       </c>
       <c r="E60" s="2">
-        <v>0.2210151412374509</v>
+        <v>0.22101514123745089</v>
       </c>
       <c r="F60" s="2">
-        <v>3.034253793375033</v>
+        <v>3.0342537933750329</v>
       </c>
       <c r="G60" s="2">
         <v>0.2222935722900386</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -1835,16 +1862,16 @@
         <v>0.4056267812470879</v>
       </c>
       <c r="E61" s="2">
-        <v>0.4690145035250251</v>
+        <v>0.46901450352502511</v>
       </c>
       <c r="F61" s="2">
-        <v>0.584356541984392</v>
+        <v>0.58435654198439202</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.023762578549592</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>-2.3762578549592E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -1855,19 +1882,19 @@
         <v>25</v>
       </c>
       <c r="D62" s="1">
-        <v>0.9882240932286304</v>
+        <v>0.98822409322863036</v>
       </c>
       <c r="E62" s="2">
-        <v>0.0442770115275558</v>
+        <v>4.4277011527555803E-2</v>
       </c>
       <c r="F62" s="2">
-        <v>41.13478123475495</v>
+        <v>41.134781234754954</v>
       </c>
       <c r="G62" s="2">
-        <v>-0.1320870330150457</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>-0.13208703301504571</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1878,19 +1905,19 @@
         <v>25</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.448336984719677</v>
+        <v>-0.44833698471967698</v>
       </c>
       <c r="E63" s="2">
         <v>2.101005881863975</v>
       </c>
       <c r="F63" s="2">
-        <v>0.0132756438737075</v>
+        <v>1.3275643873707501E-2</v>
       </c>
       <c r="G63" s="2">
-        <v>0.6938489642374671</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>0.69384896423746711</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -1901,19 +1928,19 @@
         <v>25</v>
       </c>
       <c r="D64" s="1">
-        <v>0.894578290892083</v>
+        <v>0.89457829089208296</v>
       </c>
       <c r="E64" s="2">
-        <v>0.0240689045247445</v>
+        <v>2.40689045247445E-2</v>
       </c>
       <c r="F64" s="2">
         <v>15.39949026555583</v>
       </c>
       <c r="G64" s="2">
-        <v>-0.0523630622858179</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>-5.2363062285817899E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -1924,19 +1951,19 @@
         <v>25</v>
       </c>
       <c r="D65" s="1">
-        <v>0.9807468939431072</v>
+        <v>0.98074689394310721</v>
       </c>
       <c r="E65" s="2">
-        <v>0.07239102817074571</v>
+        <v>7.2391028170745705E-2</v>
       </c>
       <c r="F65" s="2">
         <v>23.69994400161022</v>
       </c>
       <c r="G65" s="2">
-        <v>-0.1523090929007065</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>-0.15230909290070649</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -1947,19 +1974,19 @@
         <v>25</v>
       </c>
       <c r="D66" s="1">
-        <v>0.8593682597611279</v>
+        <v>0.85936825976112785</v>
       </c>
       <c r="E66" s="2">
         <v>0.1109712277521281</v>
       </c>
       <c r="F66" s="2">
-        <v>5.726659277944965</v>
+        <v>5.7266592779449654</v>
       </c>
       <c r="G66" s="2">
-        <v>-0.0069892717444375</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>-6.9892717444375004E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -1970,19 +1997,19 @@
         <v>25</v>
       </c>
       <c r="D67" s="1">
-        <v>0.846084345146916</v>
+        <v>0.84608434514691599</v>
       </c>
       <c r="E67" s="2">
-        <v>0.0351405913722205</v>
+        <v>3.5140591372220503E-2</v>
       </c>
       <c r="F67" s="2">
-        <v>11.96145862669571</v>
+        <v>11.961458626695711</v>
       </c>
       <c r="G67" s="2">
-        <v>-0.0120813956361054</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>-1.2081395636105399E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -1996,16 +2023,16 @@
         <v>0.8238711490329107</v>
       </c>
       <c r="E68" s="2">
-        <v>0.2554983790042621</v>
+        <v>0.25549837900426209</v>
       </c>
       <c r="F68" s="2">
-        <v>2.48013304385453</v>
+        <v>2.4801330438545302</v>
       </c>
       <c r="G68" s="2">
         <v>0.2169606255126949</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -2019,16 +2046,16 @@
         <v>0.8238711490329107</v>
       </c>
       <c r="E69" s="2">
-        <v>0.2554983790042621</v>
+        <v>0.25549837900426209</v>
       </c>
       <c r="F69" s="2">
-        <v>2.48013304385453</v>
+        <v>2.4801330438545302</v>
       </c>
       <c r="G69" s="2">
         <v>0.2169606255126949</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -2039,7 +2066,7 @@
         <v>24</v>
       </c>
       <c r="D70" s="1">
-        <v>0.8077205322831936</v>
+        <v>0.80772053228319363</v>
       </c>
       <c r="E70" s="2">
         <v>0.2574775655241987</v>
@@ -2048,10 +2075,10 @@
         <v>3.153223166305422</v>
       </c>
       <c r="G70" s="2">
-        <v>0.0223992751140484</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>2.2399275114048399E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2062,19 +2089,19 @@
         <v>24</v>
       </c>
       <c r="D71" s="1">
-        <v>0.9187366434110736</v>
+        <v>0.91873664341107364</v>
       </c>
       <c r="E71" s="2">
-        <v>0.0306016979705409</v>
+        <v>3.0601697970540898E-2</v>
       </c>
       <c r="F71" s="2">
         <v>16.92928272879865</v>
       </c>
       <c r="G71" s="2">
-        <v>0.004001714737785</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>4.0017147377849997E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -2085,19 +2112,19 @@
         <v>24</v>
       </c>
       <c r="D72" s="1">
-        <v>0.955660994686936</v>
+        <v>0.95566099468693599</v>
       </c>
       <c r="E72" s="2">
-        <v>0.0916778978527822</v>
+        <v>9.16778978527822E-2</v>
       </c>
       <c r="F72" s="2">
-        <v>14.37882940905081</v>
+        <v>14.378829409050811</v>
       </c>
       <c r="G72" s="2">
-        <v>0.0051126898632809</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>5.1126898632809E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -2108,19 +2135,19 @@
         <v>24</v>
       </c>
       <c r="D73" s="1">
-        <v>0.9807591650467484</v>
+        <v>0.98075916504674843</v>
       </c>
       <c r="E73" s="2">
-        <v>0.1576588633355145</v>
+        <v>0.15765886333551449</v>
       </c>
       <c r="F73" s="2">
         <v>17.38786409598838</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.0320476050467353</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>-3.2047605046735303E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -2131,19 +2158,19 @@
         <v>24</v>
       </c>
       <c r="D74" s="1">
-        <v>0.9881857290354226</v>
+        <v>0.98818572903542257</v>
       </c>
       <c r="E74" s="2">
-        <v>0.0403769221455153</v>
+        <v>4.0376922145515297E-2</v>
       </c>
       <c r="F74" s="2">
         <v>44.85503144118087</v>
       </c>
       <c r="G74" s="2">
-        <v>0.0250026558470557</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>2.5002655847055699E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -2154,19 +2181,19 @@
         <v>24</v>
       </c>
       <c r="D75" s="1">
-        <v>0.8610363972230393</v>
+        <v>0.86103639722303926</v>
       </c>
       <c r="E75" s="2">
-        <v>0.0523301322955476</v>
+        <v>5.2330132295547602E-2</v>
       </c>
       <c r="F75" s="2">
-        <v>10.56986096078749</v>
+        <v>10.569860960787491</v>
       </c>
       <c r="G75" s="2">
-        <v>-0.025864885298836</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>-2.5864885298835998E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -2177,19 +2204,19 @@
         <v>24</v>
       </c>
       <c r="D76" s="1">
-        <v>0.9147934259218892</v>
+        <v>0.91479342592188917</v>
       </c>
       <c r="E76" s="2">
         <v>0.1140984085341927</v>
       </c>
       <c r="F76" s="2">
-        <v>8.052278776312628</v>
+        <v>8.0522787763126278</v>
       </c>
       <c r="G76" s="2">
-        <v>0.003456442167271</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>3.4564421672710001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -2203,16 +2230,16 @@
         <v>0.9764576764902656</v>
       </c>
       <c r="E77" s="2">
-        <v>0.08045918079305529</v>
+        <v>8.0459180793055293E-2</v>
       </c>
       <c r="F77" s="2">
         <v>22.84517134144582</v>
       </c>
       <c r="G77" s="2">
-        <v>0.0380525192664985</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>3.8052519266498497E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -2223,19 +2250,19 @@
         <v>24</v>
       </c>
       <c r="D78" s="1">
-        <v>0.9931449679112714</v>
+        <v>0.99314496791127138</v>
       </c>
       <c r="E78" s="2">
-        <v>0.0561699411622871</v>
+        <v>5.6169941162287101E-2</v>
       </c>
       <c r="F78" s="2">
-        <v>49.16052783490608</v>
+        <v>49.160527834906077</v>
       </c>
       <c r="G78" s="2">
-        <v>-0.054937423510742</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>-5.4937423510742003E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -2246,19 +2273,19 @@
         <v>24</v>
       </c>
       <c r="D79" s="1">
-        <v>0.9722192083182772</v>
+        <v>0.97221920831827724</v>
       </c>
       <c r="E79" s="2">
-        <v>0.0574411754184301</v>
+        <v>5.74411754184301E-2</v>
       </c>
       <c r="F79" s="2">
-        <v>22.71129158512512</v>
+        <v>22.711291585125121</v>
       </c>
       <c r="G79" s="2">
-        <v>0.0147414625988766</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>1.47414625988766E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -2269,19 +2296,19 @@
         <v>25</v>
       </c>
       <c r="D80" s="1">
-        <v>0.9379260474178682</v>
+        <v>0.93792604741786822</v>
       </c>
       <c r="E80" s="2">
-        <v>0.0831219806414871</v>
+        <v>8.3121980641487098E-2</v>
       </c>
       <c r="F80" s="2">
-        <v>12.22679695034977</v>
+        <v>12.226796950349771</v>
       </c>
       <c r="G80" s="2">
-        <v>0.0049251278623743</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>4.9251278623743001E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2292,19 +2319,19 @@
         <v>25</v>
       </c>
       <c r="D81" s="1">
-        <v>0.9381919043966916</v>
+        <v>0.93819190439669164</v>
       </c>
       <c r="E81" s="2">
-        <v>0.0232753451639297</v>
+        <v>2.3275345163929699E-2</v>
       </c>
       <c r="F81" s="2">
-        <v>23.16099969248001</v>
+        <v>23.160999692480011</v>
       </c>
       <c r="G81" s="2">
-        <v>-0.0037640340279484</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>-3.7640340279484E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -2315,19 +2342,19 @@
         <v>25</v>
       </c>
       <c r="D82" s="1">
-        <v>0.9780156266769968</v>
+        <v>0.97801562667699682</v>
       </c>
       <c r="E82" s="2">
-        <v>0.0454561647838747</v>
+        <v>4.5456164783874702E-2</v>
       </c>
       <c r="F82" s="2">
         <v>30.1801784953857</v>
       </c>
       <c r="G82" s="2">
-        <v>-0.0234155236376956</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>-2.3415523637695598E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -2338,7 +2365,7 @@
         <v>25</v>
       </c>
       <c r="D83" s="1">
-        <v>0.6446419256611096</v>
+        <v>0.64464192566110956</v>
       </c>
       <c r="E83" s="2">
         <v>2.91179411982319</v>
@@ -2347,10 +2374,10 @@
         <v>0.4368981794411142</v>
       </c>
       <c r="G83" s="2">
-        <v>0.1504592287109376</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>0.15045922871093759</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -2361,19 +2388,19 @@
         <v>25</v>
       </c>
       <c r="D84" s="1">
-        <v>0.9821385725203428</v>
+        <v>0.98213857252034276</v>
       </c>
       <c r="E84" s="2">
-        <v>0.0610439246667207</v>
+        <v>6.1043924666720699E-2</v>
       </c>
       <c r="F84" s="2">
-        <v>29.54246876817109</v>
+        <v>29.542468768171091</v>
       </c>
       <c r="G84" s="2">
-        <v>-0.0101687089911665</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>-1.01687089911665E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -2387,16 +2414,16 @@
         <v>0.8649531904696377</v>
       </c>
       <c r="E85" s="2">
-        <v>0.0508551683145274</v>
+        <v>5.0855168314527403E-2</v>
       </c>
       <c r="F85" s="2">
-        <v>10.78406608021936</v>
+        <v>10.784066080219359</v>
       </c>
       <c r="G85" s="2">
-        <v>-0.008533104971144999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>-8.5331049711449992E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -2407,19 +2434,19 @@
         <v>25</v>
       </c>
       <c r="D86" s="1">
-        <v>0.9355190686874552</v>
+        <v>0.93551906868745516</v>
       </c>
       <c r="E86" s="2">
-        <v>0.08634511741804619</v>
+        <v>8.6345117418046194E-2</v>
       </c>
       <c r="F86" s="2">
-        <v>12.79523220510326</v>
+        <v>12.795232205103259</v>
       </c>
       <c r="G86" s="2">
-        <v>0.0164807450585936</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>1.64807450585936E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -2430,19 +2457,19 @@
         <v>25</v>
       </c>
       <c r="D87" s="1">
-        <v>0.9671909254291364</v>
+        <v>0.96719092542913643</v>
       </c>
       <c r="E87" s="2">
         <v>0.1121295976354432</v>
       </c>
       <c r="F87" s="2">
-        <v>15.90964297194139</v>
+        <v>15.909642971941389</v>
       </c>
       <c r="G87" s="2">
-        <v>-0.0225176037941957</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>-2.2517603794195699E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -2456,16 +2483,16 @@
         <v>0.9740753872641954</v>
       </c>
       <c r="E88" s="2">
-        <v>0.2124255515039186</v>
+        <v>0.21242555150391859</v>
       </c>
       <c r="F88" s="2">
-        <v>11.94959233813714</v>
+        <v>11.949592338137141</v>
       </c>
       <c r="G88" s="2">
-        <v>-0.0420254907017298</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>-4.2025490701729798E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -2476,19 +2503,19 @@
         <v>25</v>
       </c>
       <c r="D89" s="1">
-        <v>0.9556229585559404</v>
+        <v>0.95562295855594037</v>
       </c>
       <c r="E89" s="2">
-        <v>0.0917565435622998</v>
+        <v>9.17565435622998E-2</v>
       </c>
       <c r="F89" s="2">
-        <v>13.77468198613797</v>
+        <v>13.774681986137971</v>
       </c>
       <c r="G89" s="2">
-        <v>-0.0170309601916507</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>-1.70309601916507E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -2499,19 +2526,19 @@
         <v>25</v>
       </c>
       <c r="D90" s="1">
-        <v>0.9556229585559404</v>
+        <v>0.95562295855594037</v>
       </c>
       <c r="E90" s="2">
-        <v>0.0917565435622998</v>
+        <v>9.17565435622998E-2</v>
       </c>
       <c r="F90" s="2">
-        <v>13.77468198613797</v>
+        <v>13.774681986137971</v>
       </c>
       <c r="G90" s="2">
-        <v>-0.0170309601916507</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>-1.70309601916507E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -2522,19 +2549,19 @@
         <v>24</v>
       </c>
       <c r="D91" s="1">
-        <v>0.9884195275956456</v>
+        <v>0.98841952759564555</v>
       </c>
       <c r="E91" s="2">
-        <v>0.0347714804988237</v>
+        <v>3.4771480498823698E-2</v>
       </c>
       <c r="F91" s="2">
-        <v>47.2626126230386</v>
+        <v>47.262612623038599</v>
       </c>
       <c r="G91" s="2">
-        <v>0.0218170259574839</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>2.1817025957483901E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -2545,19 +2572,19 @@
         <v>24</v>
       </c>
       <c r="D92" s="1">
-        <v>0.8950543957778295</v>
+        <v>0.89505439577782953</v>
       </c>
       <c r="E92" s="2">
-        <v>0.08771791515682929</v>
+        <v>8.7717915156829293E-2</v>
       </c>
       <c r="F92" s="2">
-        <v>9.13054917475452</v>
+        <v>9.1305491747545204</v>
       </c>
       <c r="G92" s="2">
-        <v>0.0408901839885108</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>4.0890183988510798E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -2568,19 +2595,19 @@
         <v>24</v>
       </c>
       <c r="D93" s="1">
-        <v>0.9036866344026742</v>
+        <v>0.90368663440267416</v>
       </c>
       <c r="E93" s="2">
         <v>0.2263887329751946</v>
       </c>
       <c r="F93" s="2">
-        <v>6.00458166675157</v>
+        <v>6.0045816667515703</v>
       </c>
       <c r="G93" s="2">
-        <v>0.0472451835193097</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>4.7245183519309703E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -2591,19 +2618,19 @@
         <v>24</v>
       </c>
       <c r="D94" s="1">
-        <v>0.8931080890559389</v>
+        <v>0.89310808905593886</v>
       </c>
       <c r="E94" s="2">
-        <v>0.0893447195300601</v>
+        <v>8.9344719530060096E-2</v>
       </c>
       <c r="F94" s="2">
-        <v>9.479727384874751</v>
+        <v>9.4797273848747512</v>
       </c>
       <c r="G94" s="2">
-        <v>0.090870686646931</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>9.0870686646931001E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -2614,19 +2641,19 @@
         <v>24</v>
       </c>
       <c r="D95" s="1">
-        <v>0.9620218012234648</v>
+        <v>0.96202180122346481</v>
       </c>
       <c r="E95" s="2">
-        <v>0.1140331889778688</v>
+        <v>0.11403318897786879</v>
       </c>
       <c r="F95" s="2">
-        <v>13.98245614225396</v>
+        <v>13.982456142253961</v>
       </c>
       <c r="G95" s="2">
-        <v>0.0456264044452071</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>4.5626404445207103E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -2637,7 +2664,7 @@
         <v>24</v>
       </c>
       <c r="D96" s="1">
-        <v>0.9564808694941196</v>
+        <v>0.95648086949411959</v>
       </c>
       <c r="E96" s="2">
         <v>0.102293599172927</v>
@@ -2646,10 +2673,10 @@
         <v>14.10822659472287</v>
       </c>
       <c r="G96" s="2">
-        <v>0.0078181755716605</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>7.8181755716605003E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -2663,16 +2690,16 @@
         <v>0.980654504220006</v>
       </c>
       <c r="E97" s="2">
-        <v>0.0580867088808229</v>
+        <v>5.8086708880822902E-2</v>
       </c>
       <c r="F97" s="2">
         <v>27.89951156179924</v>
       </c>
       <c r="G97" s="2">
-        <v>0.0612494426008991</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>6.1249442600899102E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -2683,19 +2710,19 @@
         <v>25</v>
       </c>
       <c r="D98" s="1">
-        <v>0.9322614712187932</v>
+        <v>0.93226147121879321</v>
       </c>
       <c r="E98" s="2">
-        <v>0.0566186889343105</v>
+        <v>5.6618688934310497E-2</v>
       </c>
       <c r="F98" s="2">
-        <v>15.01848543870394</v>
+        <v>15.018485438703941</v>
       </c>
       <c r="G98" s="2">
-        <v>0.0598919540080421</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>5.9891954008042099E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>12</v>
       </c>
@@ -2706,19 +2733,19 @@
         <v>25</v>
       </c>
       <c r="D99" s="1">
-        <v>0.8391940456457643</v>
+        <v>0.83919404564576427</v>
       </c>
       <c r="E99" s="2">
-        <v>0.3779813532145238</v>
+        <v>0.37798135321452381</v>
       </c>
       <c r="F99" s="2">
-        <v>3.532856737961269</v>
+        <v>3.5328567379612692</v>
       </c>
       <c r="G99" s="2">
-        <v>0.1716782241382062</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>0.17167822413820619</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>12</v>
       </c>
@@ -2729,19 +2756,19 @@
         <v>25</v>
       </c>
       <c r="D100" s="1">
-        <v>0.7134804983600895</v>
+        <v>0.71348049836008953</v>
       </c>
       <c r="E100" s="2">
-        <v>0.2394849552956995</v>
+        <v>0.23948495529569949</v>
       </c>
       <c r="F100" s="2">
         <v>3.205804130832532</v>
       </c>
       <c r="G100" s="2">
-        <v>0.1138439803752296</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>0.11384398037522959</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>12</v>
       </c>
@@ -2752,19 +2779,19 @@
         <v>25</v>
       </c>
       <c r="D101" s="1">
-        <v>0.9137576824463668</v>
+        <v>0.91375768244636679</v>
       </c>
       <c r="E101" s="2">
         <v>0.2589508405427336</v>
       </c>
       <c r="F101" s="2">
-        <v>5.742349692208156</v>
+        <v>5.7423496922081556</v>
       </c>
       <c r="G101" s="2">
         <v>0.123299962271658</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>12</v>
       </c>
@@ -2775,19 +2802,19 @@
         <v>25</v>
       </c>
       <c r="D102" s="1">
-        <v>0.9078260410226416</v>
+        <v>0.90782604102264164</v>
       </c>
       <c r="E102" s="2">
-        <v>0.2166588786174768</v>
+        <v>0.21665887861747679</v>
       </c>
       <c r="F102" s="2">
         <v>6.389156896875928</v>
       </c>
       <c r="G102" s="2">
-        <v>0.0797793059863508</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>7.9779305986350801E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -2798,19 +2825,24 @@
         <v>25</v>
       </c>
       <c r="D103" s="1">
-        <v>0.9078260410226416</v>
+        <v>0.90782604102264164</v>
       </c>
       <c r="E103" s="2">
-        <v>0.2166588786174768</v>
+        <v>0.21665887861747679</v>
       </c>
       <c r="F103" s="2">
         <v>6.389156896875928</v>
       </c>
       <c r="G103" s="2">
-        <v>0.0797793059863508</v>
+        <v>7.9779305986350801E-2</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D103">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>